--- a/cotacoes/2026-09-08/fechamento/PEDIDO_PLUSFARMA_09-09-2026.xlsx
+++ b/cotacoes/2026-09-08/fechamento/PEDIDO_PLUSFARMA_09-09-2026.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +5.7% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +5.7% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.0% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +4.0% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr"/>
@@ -821,7 +821,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr"/>
@@ -884,7 +884,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.3% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +2.3% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr"/>
@@ -947,41 +947,41 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.0% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +6.0% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>150061</v>
+        <v>238761</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>162922</t>
+          <t>194379</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>7895296053044</t>
+          <t>7895296100038</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>DICLORIDRATO DE HIDROXIZINA 25MG CX 30 COMP</t>
+          <t>DROSPIRENONA+ETINILESTRADIOL 3+0,03MG CX 21 COMP REV</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>28.55</v>
+        <v>10.39</v>
       </c>
       <c r="I8" s="5">
         <f>G8*H8</f>
@@ -992,13 +992,13 @@
         <v/>
       </c>
       <c r="K8" s="5" t="n">
-        <v>26.56</v>
+        <v>10.44</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>26.56</v>
+        <v>8.948700000000001</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>26.56</v>
+        <v>9.9429</v>
       </c>
       <c r="N8" s="6">
         <f>J8/M8-1</f>
@@ -1010,41 +1010,41 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +7.5% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>238761</v>
+        <v>660351</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>194379</t>
+          <t>194328</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>7895296100038</t>
+          <t>7896472521845</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>DROSPIRENONA+ETINILESTRADIOL 3+0,03MG CX 21 COMP REV</t>
+          <t>EZETIMIBA 10MG 30 CPR</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>10.39</v>
+        <v>16.49</v>
       </c>
       <c r="I9" s="5">
         <f>G9*H9</f>
@@ -1055,13 +1055,13 @@
         <v/>
       </c>
       <c r="K9" s="5" t="n">
-        <v>10.44</v>
+        <v>15.99</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>8.948700000000001</v>
+        <v>15.99</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>9.9429</v>
+        <v>15.99</v>
       </c>
       <c r="N9" s="6">
         <f>J9/M9-1</f>
@@ -1073,41 +1073,41 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ últ. compra)</t>
+          <t>REAJUSTE +3.1% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>660351</v>
+        <v>630321</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>194328</t>
+          <t>179620</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>7896472521845</t>
+          <t>7898687735918</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>EZETIMIBA 10MG 30 CPR</t>
+          <t>IROSE  NITAZOXANIDA 20MG/ML PO SUS OR FR 100ML+SER DOS</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>16.49</v>
+        <v>15.11</v>
       </c>
       <c r="I10" s="5">
         <f>G10*H10</f>
@@ -1118,13 +1118,13 @@
         <v/>
       </c>
       <c r="K10" s="5" t="n">
-        <v>15.99</v>
+        <v>14.56</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>15.99</v>
+        <v>14.56</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>15.99</v>
+        <v>14.56</v>
       </c>
       <c r="N10" s="6">
         <f>J10/M10-1</f>
@@ -1136,41 +1136,41 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.1% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +3.8% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>249001</v>
+        <v>336001</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>194280</t>
+          <t>132721</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>7895296276047</t>
+          <t>7898945030212</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>FINASTERIDA 5MG CX 30 COMP REV</t>
+          <t>MALEATO DE TRIMEBUTINA 200MG CX 30 COMP</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>19.99</v>
+        <v>34.66</v>
       </c>
       <c r="I11" s="5">
         <f>G11*H11</f>
@@ -1181,13 +1181,13 @@
         <v/>
       </c>
       <c r="K11" s="5" t="n">
-        <v>18.78</v>
+        <v>33.8</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>18.78</v>
+        <v>31.95</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>18.78</v>
+        <v>33.18333333333333</v>
       </c>
       <c r="N11" s="6">
         <f>J11/M11-1</f>
@@ -1199,41 +1199,41 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +6.4% (aceito, lim 10% zerado)</t>
+          <t>REAJUSTE +2.5% vs últ. (≤4%)</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>630321</v>
+        <v>652061</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>179620</t>
+          <t>184640</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>7898687735918</t>
+          <t>7891317029951</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>IROSE  NITAZOXANIDA 20MG/ML PO SUS OR FR 100ML+SER DOS</t>
+          <t>MAQ SENIOR PREMIUM 30CPR-DEMAIS PROD</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>15.11</v>
+        <v>39.15</v>
       </c>
       <c r="I12" s="5">
         <f>G12*H12</f>
@@ -1244,13 +1244,13 @@
         <v/>
       </c>
       <c r="K12" s="5" t="n">
-        <v>14.56</v>
+        <v>40.97</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>14.56</v>
+        <v>40.97</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>14.56</v>
+        <v>40.97</v>
       </c>
       <c r="N12" s="6">
         <f>J12/M12-1</f>
@@ -1262,28 +1262,28 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +3.8% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>336001</v>
+        <v>388861</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>132721</t>
+          <t>193720</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>7898945030212</t>
+          <t>7895296199025</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>MALEATO DE TRIMEBUTINA 200MG CX 30 COMP</t>
+          <t>PANTOPRAZOL 20MG CX 4BL X 7 COMP REV</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -1296,7 +1296,7 @@
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>34.66</v>
+        <v>4.69</v>
       </c>
       <c r="I13" s="5">
         <f>G13*H13</f>
@@ -1307,13 +1307,13 @@
         <v/>
       </c>
       <c r="K13" s="5" t="n">
-        <v>33.8</v>
+        <v>6.5</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>31.95</v>
+        <v>6.38</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>33.18333333333333</v>
+        <v>6.419999999999999</v>
       </c>
       <c r="N13" s="6">
         <f>J13/M13-1</f>
@@ -1325,41 +1325,41 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +2.5% (aceito, lim 5%)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>652061</v>
+        <v>407821</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>184640</t>
+          <t>190837</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>7891317029951</t>
+          <t>7898569765347</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>MAQ SENIOR PREMIUM 30CPR-DEMAIS PROD</t>
+          <t>PREDNISOLONA 5MG CX 10 COMP</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>39.15</v>
+        <v>4.22</v>
       </c>
       <c r="I14" s="5">
         <f>G14*H14</f>
@@ -1370,13 +1370,13 @@
         <v/>
       </c>
       <c r="K14" s="5" t="n">
-        <v>40.97</v>
+        <v>4.32</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>40.97</v>
+        <v>4.32</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>40.97</v>
+        <v>4.32</v>
       </c>
       <c r="N14" s="6">
         <f>J14/M14-1</f>
@@ -1388,41 +1388,41 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>388861</v>
+        <v>409221</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>193720</t>
+          <t>193518</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>7895296199025</t>
+          <t>7895296286022</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>PANTOPRAZOL 20MG CX 4BL X 7 COMP REV</t>
+          <t>PREDNISONA 5MG CX 20 COMP</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>4.69</v>
+        <v>4.49</v>
       </c>
       <c r="I15" s="5">
         <f>G15*H15</f>
@@ -1433,13 +1433,13 @@
         <v/>
       </c>
       <c r="K15" s="5" t="n">
-        <v>6.5</v>
+        <v>4.28</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>6.38</v>
+        <v>4.28</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>6.419999999999999</v>
+        <v>4.28</v>
       </c>
       <c r="N15" s="6">
         <f>J15/M15-1</f>
@@ -1451,41 +1451,41 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>REAJUSTE +4.9% vs média (≤6%)</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>407821</v>
+        <v>457261</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>190837</t>
+          <t>193143</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>7898569765347</t>
+          <t>7895296240031</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>PREDNISOLONA 5MG CX 10 COMP</t>
+          <t>TADALAFILA 5MG CX 2BL X 15 COMP REV</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>4.22</v>
+        <v>3.69</v>
       </c>
       <c r="I16" s="5">
         <f>G16*H16</f>
@@ -1496,13 +1496,13 @@
         <v/>
       </c>
       <c r="K16" s="5" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>4.32</v>
+        <v>3.74</v>
       </c>
       <c r="N16" s="6">
         <f>J16/M16-1</f>
@@ -1514,41 +1514,41 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>409221</v>
+        <v>462441</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>193518</t>
+          <t>193135</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>7895296286022</t>
+          <t>7895296132039</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>PREDNISONA 5MG CX 20 COMP</t>
+          <t>TIBOLONA 2,5MG  CX 30 COMP</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>4.49</v>
+        <v>24.85</v>
       </c>
       <c r="I17" s="5">
         <f>G17*H17</f>
@@ -1559,13 +1559,13 @@
         <v/>
       </c>
       <c r="K17" s="5" t="n">
-        <v>4.28</v>
+        <v>25.2</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>4.28</v>
+        <v>24.21</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>4.28</v>
+        <v>24.54</v>
       </c>
       <c r="N17" s="6">
         <f>J17/M17-1</f>
@@ -1577,28 +1577,28 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>REAJUSTE +4.9% (aceito, lim 10% zerado)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>457261</v>
+        <v>648221</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>193143</t>
+          <t>204820</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>7895296240031</t>
+          <t>6939184632407</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>TADALAFILA 5MG CX 2BL X 15 COMP REV</t>
+          <t>TIRA DE TESTE DE GLICOSE C/50 UND</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1611,7 +1611,7 @@
         <v>2</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>3.69</v>
+        <v>29.9</v>
       </c>
       <c r="I18" s="5">
         <f>G18*H18</f>
@@ -1622,13 +1622,13 @@
         <v/>
       </c>
       <c r="K18" s="5" t="n">
-        <v>3.74</v>
+        <v>44.53</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>3.74</v>
+        <v>44.53</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>3.74</v>
+        <v>44.53</v>
       </c>
       <c r="N18" s="6">
         <f>J18/M18-1</f>
@@ -1640,41 +1640,41 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>OK (≤ menor hist.)</t>
+          <t>OK (≤ últ. compra)</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>462441</v>
+        <v>662781</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>193135</t>
+          <t>192929</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>7895296132039</t>
+          <t>7896472521784</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>TIBOLONA 2,5MG  CX 30 COMP</t>
+          <t>VALSARTANA 320MG 30 COM-NQ</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>24.85</v>
+        <v>25.05</v>
       </c>
       <c r="I19" s="5">
         <f>G19*H19</f>
@@ -1685,13 +1685,13 @@
         <v/>
       </c>
       <c r="K19" s="5" t="n">
-        <v>25.2</v>
+        <v>25.39</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>24.21</v>
+        <v>25.39</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>24.54</v>
+        <v>25.39</v>
       </c>
       <c r="N19" s="6">
         <f>J19/M19-1</f>
@@ -1709,146 +1709,20 @@
       <c r="Q19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>648221</v>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>204820</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>6939184632407</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>TIRA DE TESTE DE GLICOSE C/50 UND</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="I20" s="5">
-        <f>G20*H20</f>
-        <v/>
-      </c>
-      <c r="J20" s="5">
-        <f>H20/E20</f>
-        <v/>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>44.53</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>44.53</v>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v>44.53</v>
-      </c>
-      <c r="N20" s="6">
-        <f>J20/M20-1</f>
-        <v/>
-      </c>
-      <c r="O20" s="6">
-        <f>J20/K20-1</f>
-        <v/>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>662781</v>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>192929</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>7896472521784</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>VALSARTANA 320MG 30 COM-NQ</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>25.05</v>
-      </c>
-      <c r="I21" s="5">
-        <f>G21*H21</f>
-        <v/>
-      </c>
-      <c r="J21" s="5">
-        <f>H21/E21</f>
-        <v/>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>25.39</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>25.39</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v>25.39</v>
-      </c>
-      <c r="N21" s="6">
-        <f>J21/M21-1</f>
-        <v/>
-      </c>
-      <c r="O21" s="6">
-        <f>J21/K21-1</f>
-        <v/>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>OK (≤ menor hist.)</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="I20" s="8">
+        <f>SUM(I2:I19)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="I22" s="8">
-        <f>SUM(I2:I21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Pedido FINAL PLUSFARMA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: preço até 5% acima da referência (últ. compra; sem ela, menor histórico), 10% quando o item está zerado. 'Qtd pedido' na embalagem do fornecedor.</t>
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Pedido FINAL PLUSFARMA — cotação 08/09/2026 (fechada 09/09). Somente itens aprovados: teto de reajuste de 4% sobre a última compra OU 6% sobre a média histórica (3/6/12m). 'Qtd pedido' na embalagem do fornecedor.</t>
         </is>
       </c>
     </row>
